--- a/inwon-app/withdraw_template.xlsx
+++ b/inwon-app/withdraw_template.xlsx
@@ -441,7 +441,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>개인 사유</t>
+          <t>타학원 이동</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -542,7 +542,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="퇴원사유" prompt="목록에서 선택하세요" type="list">
-      <formula1>"타학원 이동,개인 사유,학습 부담,담임 불만,교우 관계,스케줄,이사,졸업,폐강,기타"</formula1>
+      <formula1>"타학원 이동,담임 불만,스케줄(시간이동 불가) / 폐강,교우 관계,이사 / 어학연수 / 캠프 / 여행(장기),졸업,차량 불만,학원비 부담,성적 불만족,건강상의 문제"</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="전출분원" prompt="전출인 경우에만 분원 선택 (일반 퇴원은 비워두세요)" type="list">
       <formula1>"서수원분원,수원분원,장안분원,남동탄분원,운정1분원,운정2분원"</formula1>
